--- a/agent_learning/03_noi_agent/evals/aichat/ad_hoc_runs/dialogue_state_v3_repair_fairness_addon_20260516/coach_response_review_workbook_dialogue_state_v3_dbox_repair_addon_by_case_20260516.zh.xlsx
+++ b/agent_learning/03_noi_agent/evals/aichat/ad_hoc_runs/dialogue_state_v3_repair_fairness_addon_20260516/coach_response_review_workbook_dialogue_state_v3_dbox_repair_addon_by_case_20260516.zh.xlsx
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>先看“评分流程”，再进入“盲评表”。盲评表中只评价“AI 回复（要评分）”，不要评价近期对话或上一轮 AI 提示本身。</t>
+          <t>先看“评分流程”和“评分说明”，再看“按题索引”。推荐逐个打开“题001_...”到“题050_...”这些按题 sheet，横向比较同一题的 7 条匿名 AI 回复，只填写黄色评分列。“盲评表”用于全局汇总查看，除非脚本指定，不建议人工直接填写。</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_0abd4353c4</t>
+          <t>resp_40175690d7</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -8072,29 +8072,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -8741,7 +8772,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_22db4f0308</t>
+          <t>resp_56e5c76d8d</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -8834,29 +8865,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -9511,7 +9573,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_613d2aca29</t>
+          <t>resp_184237193c</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -9623,29 +9685,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -10300,7 +10393,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_02ab4c08d4</t>
+          <t>resp_5f0f43581d</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -10417,29 +10510,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -11094,7 +11218,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_a0c5c7b461</t>
+          <t>resp_3a7ef37ca1</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -11207,29 +11331,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -11884,7 +12039,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_ece2ca97b1</t>
+          <t>resp_230001326e</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -11976,29 +12131,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生只比较相邻两个人 A、B 交换前后的等待时间贡献。
+- 回复引导学生找出哪个局部顺序不会让总等待时间变大。
+- 回复不直接给完整排序规则证明或完整贪心结论。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把两个相邻人的顺序交换与总等待时间变化连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生只比较相邻两个人 A、B 交换前后的等待时间贡献。
+- 回复引导学生找出哪个局部顺序不会让总等待时间变大。
+- 回复不直接给完整排序规则证明或完整贪心结论。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -12653,7 +12839,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_da3a8845ad</t>
+          <t>resp_ffcd15b7ee</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -12747,29 +12933,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -13424,7 +13641,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_5c778bb125</t>
+          <t>resp_b9e467565c</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -13525,29 +13742,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -14202,7 +14450,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_6d6c5dfa55</t>
+          <t>resp_2a9e80552a</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -14310,29 +14558,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -14987,7 +15266,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_da9119be87</t>
+          <t>resp_12aeaa5f9f</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -15098,29 +15377,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -15775,7 +16085,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_864ae6cae6</t>
+          <t>resp_def0d754c1</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -15874,29 +16184,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -15946,7 +16287,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>resp_291ed22177</t>
+          <t>resp_38de155161</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -16041,29 +16382,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr"/>
@@ -16105,7 +16477,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>resp_f311cc8862</t>
+          <t>resp_a42ada0f17</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -16192,29 +16564,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="6" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X5" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y5" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z5" s="6" t="inlineStr">
@@ -16264,7 +16667,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>resp_0abd4353c4</t>
+          <t>resp_40175690d7</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -16347,29 +16750,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr"/>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X6" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y6" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z6" s="6" t="inlineStr"/>
@@ -16411,7 +16845,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>resp_22db4f0308</t>
+          <t>resp_56e5c76d8d</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -16504,29 +16938,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X7" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y7" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z7" s="6" t="inlineStr">
@@ -16576,7 +17041,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>resp_613d2aca29</t>
+          <t>resp_184237193c</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -16688,29 +17153,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X8" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y8" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z8" s="6" t="inlineStr">
@@ -16760,7 +17256,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>resp_02ab4c08d4</t>
+          <t>resp_5f0f43581d</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -16877,29 +17373,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X9" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y9" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z9" s="6" t="inlineStr">
@@ -16949,7 +17476,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>resp_a0c5c7b461</t>
+          <t>resp_3a7ef37ca1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -17062,29 +17589,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="6" t="inlineStr"/>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X10" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y10" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z10" s="6" t="inlineStr">
@@ -17134,7 +17692,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>resp_ece2ca97b1</t>
+          <t>resp_230001326e</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -17226,29 +17784,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="6" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生只比较相邻两个人 A、B 交换前后的等待时间贡献。
+- 回复引导学生找出哪个局部顺序不会让总等待时间变大。
+- 回复不直接给完整排序规则证明或完整贪心结论。</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把两个相邻人的顺序交换与总等待时间变化连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生只比较相邻两个人 A、B 交换前后的等待时间贡献。
+- 回复引导学生找出哪个局部顺序不会让总等待时间变大。
+- 回复不直接给完整排序规则证明或完整贪心结论。</t>
+        </is>
+      </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X11" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -17298,7 +17887,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>resp_da3a8845ad</t>
+          <t>resp_ffcd15b7ee</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -17392,29 +17981,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr"/>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="6" t="inlineStr"/>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="6" t="inlineStr"/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y12" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z12" s="6" t="inlineStr">
@@ -17464,7 +18084,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>resp_5c778bb125</t>
+          <t>resp_b9e467565c</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -17565,29 +18185,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6" t="inlineStr"/>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="6" t="inlineStr"/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X13" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y13" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z13" s="6" t="inlineStr">
@@ -17637,7 +18288,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>resp_6d6c5dfa55</t>
+          <t>resp_2a9e80552a</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -17745,29 +18396,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="inlineStr"/>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y14" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z14" s="6" t="inlineStr">
@@ -17817,7 +18499,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>resp_da9119be87</t>
+          <t>resp_12aeaa5f9f</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -17928,29 +18610,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr"/>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="6" t="inlineStr"/>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y15" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z15" s="6" t="inlineStr">
@@ -18000,7 +18713,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>resp_26db19c2f1</t>
+          <t>resp_ecd4120ead</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -18099,29 +18812,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="6" t="inlineStr"/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X16" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y16" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z16" s="6" t="inlineStr">
@@ -18171,7 +18915,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>resp_69799698b4</t>
+          <t>resp_5b03d46937</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -18293,29 +19037,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr"/>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="6" t="inlineStr"/>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y17" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z17" s="6" t="inlineStr">
@@ -18365,7 +19140,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>resp_bf59e73177</t>
+          <t>resp_f4aab279a2</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -18474,29 +19249,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr"/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X18" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y18" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z18" s="6" t="inlineStr"/>
@@ -18538,7 +19344,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>resp_8cc7dd9d04</t>
+          <t>resp_be4295aebf</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -18632,29 +19438,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="6" t="inlineStr"/>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="6" t="inlineStr"/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X19" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y19" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z19" s="6" t="inlineStr"/>
@@ -18696,7 +19533,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>resp_5c2015e098</t>
+          <t>resp_10ded05bc6</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -18780,29 +19617,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr"/>
-      <c r="R20" s="6" t="inlineStr"/>
-      <c r="S20" s="6" t="inlineStr"/>
-      <c r="T20" s="6" t="inlineStr"/>
-      <c r="U20" s="6" t="inlineStr"/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X20" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y20" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z20" s="6" t="inlineStr"/>
@@ -18844,7 +19712,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>resp_d1fa2ec4ad</t>
+          <t>resp_c653243908</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -18978,29 +19846,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X21" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y21" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z21" s="6" t="inlineStr">
@@ -19054,7 +19953,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>resp_e2e72e663d</t>
+          <t>resp_bf657dfb52</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -19172,29 +20071,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先请学生把“前面某个状态”具体化成一个前驱来源。
+- 回复让学生用题面动作或选择说出当前量从哪里来。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先请学生把“前面某个状态”具体化成一个前驱来源。
+- 回复让学生用题面动作或选择说出当前量从哪里来。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y22" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z22" s="6" t="inlineStr">
@@ -19244,7 +20174,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>resp_ac07513099</t>
+          <t>resp_a8ea8cfb93</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -19361,29 +20291,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y23" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z23" s="6" t="inlineStr">
@@ -19433,7 +20394,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>resp_0ccf323acf</t>
+          <t>resp_12538cb899</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -19557,29 +20518,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y24" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z24" s="6" t="inlineStr">
@@ -19629,7 +20621,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>resp_6d38a918eb</t>
+          <t>resp_4c2337a2ce</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -19719,29 +20711,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y25" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z25" s="6" t="inlineStr">
@@ -19791,7 +20814,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>resp_295f5ca49e</t>
+          <t>resp_a6a3e3c23a</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -19886,29 +20909,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y26" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z26" s="6" t="inlineStr">
@@ -19958,7 +21012,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>resp_7145f451a8</t>
+          <t>resp_2d53bcd45b</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -20065,29 +21119,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y27" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z27" s="6" t="inlineStr">
@@ -20137,7 +21222,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>resp_0736fc8a27</t>
+          <t>resp_aa13f512a8</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -20226,29 +21311,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y28" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr"/>
@@ -20290,7 +21406,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>resp_c720d75aab</t>
+          <t>resp_1e28ff5948</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -20414,29 +21530,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先选一个最小方块或一个字符位置，让学生判断它对应题面中的哪一格、哪条边或哪个角。
+- 回复把注意力放在输出坐标、字符位置和题面对象的局部映射上。
+- 回复不直接给完整画图代码或完整字符模板。</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把输出图中单个字符位置、题面方块的格子/边/角以及循环坐标对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先选一个最小方块或一个字符位置，让学生判断它对应题面中的哪一格、哪条边或哪个角。
+- 回复把注意力放在输出坐标、字符位置和题面对象的局部映射上。
+- 回复不直接给完整画图代码或完整字符模板。</t>
+        </is>
+      </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y29" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -20486,7 +21633,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>resp_1394864bf9</t>
+          <t>resp_314b412a63</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -20591,29 +21738,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生固定其他人，只比较相邻两个大臣交换前后的局部最坏奖励。
+- 回复引导学生观察交换只影响这两个位置相关的奖励项。
+- 回复不直接给完整排序关键字或完整交换证明。</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把相邻两个大臣交换前后的局部最坏奖励与全局最大值控制连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生固定其他人，只比较相邻两个大臣交换前后的局部最坏奖励。
+- 回复引导学生观察交换只影响这两个位置相关的奖励项。
+- 回复不直接给完整排序关键字或完整交换证明。</t>
+        </is>
+      </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z30" s="6" t="inlineStr">
@@ -20663,7 +21841,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>resp_7a22663f04</t>
+          <t>resp_0b7421b512</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -20752,29 +21930,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y31" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z31" s="6" t="inlineStr"/>
@@ -20816,7 +22025,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>resp_2271e917ef</t>
+          <t>resp_17ab2684d7</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -20923,29 +22132,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y32" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z32" s="6" t="inlineStr">
@@ -20995,7 +22235,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>resp_4e925bcc67</t>
+          <t>resp_85f24ca560</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -21094,29 +22334,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y33" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -21172,7 +22443,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>resp_a2db97004b</t>
+          <t>resp_6ead24b915</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -21257,29 +22528,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U34" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z34" s="6" t="inlineStr"/>
@@ -21321,7 +22623,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>resp_663120cf72</t>
+          <t>resp_ef75cfbc88</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -21408,29 +22710,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y35" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -21480,7 +22813,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>resp_271835fa3c</t>
+          <t>resp_1e76bd3c79</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -21569,29 +22902,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y36" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z36" s="6" t="inlineStr">
@@ -21641,7 +23005,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>resp_ce3430ca15</t>
+          <t>resp_2e87451f57</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -21742,29 +23106,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U37" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y37" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z37" s="6" t="inlineStr">
@@ -21814,7 +23209,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>resp_6646fa85b7</t>
+          <t>resp_be280eaafc</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -21909,29 +23304,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -21981,7 +23407,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>resp_dce04287bd</t>
+          <t>resp_317903ec32</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -22074,29 +23500,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U39" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y39" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -22146,7 +23603,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>resp_6eb2ccab34</t>
+          <t>resp_6404042cb7</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -22243,29 +23700,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U40" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y40" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -22315,7 +23803,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>resp_cdb7ce8d5c</t>
+          <t>resp_0db1817a15</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -22405,29 +23893,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y41" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z41" s="6" t="inlineStr">
@@ -22477,7 +23996,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>resp_f4591e4e29</t>
+          <t>resp_755240f381</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -22560,29 +24079,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X42" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y42" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z42" s="6" t="inlineStr"/>
@@ -22624,7 +24174,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>resp_8028ab808d</t>
+          <t>resp_b2f2d2476e</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -22716,29 +24266,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W43" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X43" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y43" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr"/>
@@ -22780,7 +24361,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>resp_9e3362e1ff</t>
+          <t>resp_b138d84957</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -22870,29 +24451,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+- 回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+- 回复不直接给完整背包模板或循环方向结论。</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环方向、上一轮旧值和本轮新值复用风险对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+- 回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+- 回复不直接给完整背包模板或循环方向结论。</t>
+        </is>
+      </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y44" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z44" s="6" t="inlineStr">
@@ -22942,7 +24554,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>resp_9d0f4a61d6</t>
+          <t>resp_c19ba3145b</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -23031,29 +24643,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+- 回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+- 回复不直接给完整代码、整张字符映射表或整题总做法。</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接给出完整按键映射表</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面中的单个字符（字母或空格）映射到按键次数，并把输入逐字符累计的实现桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接给出完整按键映射表</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+- 回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+- 回复不直接给完整代码、整张字符映射表或整题总做法。</t>
+        </is>
+      </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W45" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X45" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y45" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z45" s="6" t="inlineStr">
@@ -23103,7 +24746,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>resp_1a89782c2a</t>
+          <t>resp_c1703bea82</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -23208,29 +24851,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update 后哪些前缀/摘要信息应随之改变。
+- 回复用一个极小数组检查 query 需要从哪些维护量组合出区间和。
+- 回复不直接给完整树状数组模板或完整 lowbit 操作序列。</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把单点修改、前缀和查询以及数据结构内部维护的摘要量对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update 后哪些前缀/摘要信息应随之改变。
+- 回复用一个极小数组检查 query 需要从哪些维护量组合出区间和。
+- 回复不直接给完整树状数组模板或完整 lowbit 操作序列。</t>
+        </is>
+      </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X46" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y46" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z46" s="6" t="inlineStr">
@@ -23280,7 +24954,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>resp_2b76a7077c</t>
+          <t>resp_e080ab04b3</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -23372,29 +25046,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W47" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X47" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y47" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z47" s="6" t="inlineStr">
@@ -23447,7 +25152,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>resp_18c400626b</t>
+          <t>resp_efbdc5d54e</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -23544,29 +25249,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X48" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y48" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z48" s="6" t="inlineStr">
@@ -23616,7 +25352,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>resp_58dc28c0db</t>
+          <t>resp_b3a455b71f</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -23714,29 +25450,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X49" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y49" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z49" s="6" t="inlineStr">
@@ -23786,7 +25553,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>resp_5eb05f77bd</t>
+          <t>resp_223aeebd7a</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -23884,29 +25651,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X50" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y50" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z50" s="6" t="inlineStr">
@@ -23956,7 +25754,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>resp_022dc36be8</t>
+          <t>resp_0f7146b55f</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -24079,29 +25877,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U51" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X51" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y51" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z51" s="6" t="inlineStr">
@@ -24151,7 +25980,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>resp_781f0e54ae</t>
+          <t>resp_e5a50f1ac5</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -24265,29 +26094,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X52" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y52" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z52" s="6" t="inlineStr">
@@ -24942,7 +26802,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_26db19c2f1</t>
+          <t>resp_ecd4120ead</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -25041,29 +26901,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -25718,7 +27609,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_69799698b4</t>
+          <t>resp_5b03d46937</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -25840,29 +27731,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -26517,7 +28439,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_bf59e73177</t>
+          <t>resp_f4aab279a2</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -26626,29 +28548,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -27295,7 +29248,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_8cc7dd9d04</t>
+          <t>resp_be4295aebf</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -27389,29 +29342,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -28058,7 +30042,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_5c2015e098</t>
+          <t>resp_10ded05bc6</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -28142,29 +30126,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -28811,7 +30826,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_d1fa2ec4ad</t>
+          <t>resp_c653243908</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -28945,29 +30960,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -29626,7 +31672,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_e2e72e663d</t>
+          <t>resp_bf657dfb52</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -29744,29 +31790,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先请学生把“前面某个状态”具体化成一个前驱来源。
+- 回复让学生用题面动作或选择说出当前量从哪里来。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先请学生把“前面某个状态”具体化成一个前驱来源。
+- 回复让学生用题面动作或选择说出当前量从哪里来。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -30421,7 +32498,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_ac07513099</t>
+          <t>resp_a8ea8cfb93</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -30538,29 +32615,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -31215,7 +33323,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_0ccf323acf</t>
+          <t>resp_12538cb899</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -31339,29 +33447,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -32016,7 +34155,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_6d38a918eb</t>
+          <t>resp_4c2337a2ce</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -32106,29 +34245,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -34338,7 +36508,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_295f5ca49e</t>
+          <t>resp_a6a3e3c23a</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -34433,29 +36603,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -35110,7 +37311,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_7145f451a8</t>
+          <t>resp_2d53bcd45b</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -35217,29 +37418,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -35894,7 +38126,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_0736fc8a27</t>
+          <t>resp_aa13f512a8</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -35983,29 +38215,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -36652,7 +38915,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_c720d75aab</t>
+          <t>resp_1e28ff5948</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -36776,29 +39039,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先选一个最小方块或一个字符位置，让学生判断它对应题面中的哪一格、哪条边或哪个角。
+- 回复把注意力放在输出坐标、字符位置和题面对象的局部映射上。
+- 回复不直接给完整画图代码或完整字符模板。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把输出图中单个字符位置、题面方块的格子/边/角以及循环坐标对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先选一个最小方块或一个字符位置，让学生判断它对应题面中的哪一格、哪条边或哪个角。
+- 回复把注意力放在输出坐标、字符位置和题面对象的局部映射上。
+- 回复不直接给完整画图代码或完整字符模板。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -37453,7 +39747,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_1394864bf9</t>
+          <t>resp_314b412a63</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -37558,29 +39852,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生固定其他人，只比较相邻两个大臣交换前后的局部最坏奖励。
+- 回复引导学生观察交换只影响这两个位置相关的奖励项。
+- 回复不直接给完整排序关键字或完整交换证明。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把相邻两个大臣交换前后的局部最坏奖励与全局最大值控制连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生固定其他人，只比较相邻两个大臣交换前后的局部最坏奖励。
+- 回复引导学生观察交换只影响这两个位置相关的奖励项。
+- 回复不直接给完整排序关键字或完整交换证明。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -38235,7 +40560,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_7a22663f04</t>
+          <t>resp_0b7421b512</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -38324,29 +40649,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -38993,7 +41349,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_2271e917ef</t>
+          <t>resp_17ab2684d7</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -39100,29 +41456,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把局部选择与全局目标、不变量或交换论证连接起来的正确性桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整证明
+- 不要直接给出完整交换论证或贪心正确性论证
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先比较两个局部选择的后果。
+- 回复引导学生寻找保持不变的量或可以交换的局部结构。
+- 回复不直接给完整证明。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -39777,7 +42164,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_4e925bcc67</t>
+          <t>resp_85f24ca560</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -39876,29 +42263,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先用最小样例核对一个下标、初始值或类型范围。
+- 回复把注意力放在一个实现边界上。
+- 回复不直接给完整代码补丁。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -40559,7 +42977,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_a2db97004b</t>
+          <t>resp_6ead24b915</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -40644,29 +43062,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -41313,7 +43762,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_663120cf72</t>
+          <t>resp_ef75cfbc88</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -41400,29 +43849,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -41546,7 +44026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -41574,202 +44054,219 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>0. 校准轮</t>
+          <t>正式评分入口</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>5 条 calibration samples</t>
+          <t>按题索引、题001_... 到 题050_...</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>正式评审前，两位教练先独立看 5 条，再讨论边界：major leakage、合理概念解释、安全但帮助不足、学生回复负担、微型例子是否泄露。校准样本不进 headline 结果。</t>
+          <t>正式评分优先在各“题xxx_...”sheet 中填写。同一题内 7 条匿名回复应横向比较后评分；“盲评表”主要用于全局查看和脚本汇总，不建议人工直接填写。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>1. 先看题目/题面摘要</t>
+          <t>0. 校准轮</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>题目编号、原题链接、原题题面/必要题面、题目/上下文</t>
+          <t>5 条 calibration samples</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>先理解这道题大概在考什么，不需要完整解题；如果题面不足以判断，请在备注里说明。</t>
+          <t>正式评审前，两位教练先独立看 5 条，再讨论边界：major leakage、合理概念解释、安全但帮助不足、学生回复负担、微型例子是否泄露。校准样本不进 headline 结果。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>1.5 看 case-specific rubric</t>
+          <t>1. 先看题目/题面摘要</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>本 case 成功标准、本轮禁止补完、关键桥泄露边界、允许透露、期望学生下一步</t>
+          <t>题目编号、原题链接、原题题面/必要题面、题目/上下文</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>这些字段是本轮评分的样本专属依据。先用它们确定“什么算推进”和“什么算泄露”，再看目标 AI 回复。</t>
+          <t>先理解这道题大概在考什么，不需要完整解题；如果题面不足以判断，请在备注里说明。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2. 再看近期对话</t>
+          <t>1.5 看 case-specific rubric</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>近期对话</t>
+          <t>本 case 成功标准、本轮禁止补完、关键桥泄露边界、允许透露、期望学生下一步</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>只用于理解学生为什么会问当前这句话。不要给近期对话本身打分。</t>
+          <t>这些字段是本轮评分的样本专属依据。先用它们确定“什么算推进”和“什么算泄露”，再看目标 AI 回复。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>3. 看上下文 AI 回复</t>
+          <t>2. 再看近期对话</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>上下文 AI 回复</t>
+          <t>近期对话</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>这是从近期对话自动抽取的派生显示字段，帮助快速理解学生当前短回复在回答哪个 AI 问题；它不是额外模型输入，也不是独立数据来源。</t>
+          <t>只用于理解学生为什么会问当前这句话。不要给近期对话本身打分。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>4. 看学生当前问题</t>
+          <t>3. 看上下文 AI 回复</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>学生当前问题</t>
+          <t>上下文 AI 回复</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>这是本轮 AI 必须回应的核心。评分时优先判断 AI 有没有接住这一句。</t>
+          <t>这是从近期对话自动抽取的派生显示字段，帮助快速理解学生当前短回复在回答哪个 AI 问题；它不是额外模型输入，也不是独立数据来源。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>5. 最后只评价 AI 回复（要评分）</t>
+          <t>4. 看学生当前问题</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>AI 回复（要评分）和黄色评分列</t>
+          <t>学生当前问题</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>先填主指标：总体质量、是否愿意给学生看、泄露标签、透露正当性、帮助是否足够、学生回复负担；再填诊断指标。</t>
+          <t>这是本轮 AI 必须回应的核心。评分时优先判断 AI 有没有接住这一句。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>6. 补强制备注</t>
+          <t>5. 最后只评价 AI 回复（要评分）</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>AI 回复（要评分）和黄色评分列</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>如果标了重大泄露、答案泄露、不愿给学生看、总体质量 1/2、同题最好/最差、低置信或需要讨论，请写一句原因。表格会提示应写备注但为空的格子。</t>
+          <t>先填主指标：总体质量、是否愿意给学生看、泄露标签、透露正当性、帮助是否足够、学生回复负担；再填诊断指标。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>7. 标置信与讨论</t>
+          <t>6. 补强制备注</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>评分置信度、是否需要讨论、评审状态</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>低置信、上下文错配、多桥梁或边界泄露样本应进入复评/裁决；不要把单一教练低置信标签当最终结论。</t>
+          <t>如果标了重大泄露、答案泄露、不愿给学生看、总体质量 1/2、同题最好/最差、低置信或需要讨论，请写一句原因。表格会提示应写备注但为空的格子。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>异常 A：上下文不接</t>
+          <t>7. 标置信与讨论</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>近期对话 + 学生当前问题 + 上下文对齐状态</t>
+          <t>评分置信度、是否需要讨论、评审状态</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>如果近期对话和学生当前问题明显不接，标记“是否需要讨论”，备注说明“上下文疑似错配”，不要强行低分或高分。</t>
+          <t>低置信、上下文错配、多桥梁或边界泄露样本应进入复评/裁决；不要把单一教练低置信标签当最终结论。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>异常 B：AI 没接学生当前问题</t>
+          <t>异常 A：上下文不接</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>学生当前问题 + AI 回复（要评分）</t>
+          <t>近期对话 + 学生当前问题 + 上下文对齐状态</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>如果 AI 回复只讲题面或泛泛讲算法，没有回应学生当前问题，“是否贴合题目/对话”和“是否抓住卡点”应降分。</t>
+          <t>如果近期对话和学生当前问题明显不接，标记“是否需要讨论”，备注说明“上下文疑似错配”，不要强行低分或高分。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>异常 B：AI 没接学生当前问题</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>学生当前问题 + AI 回复（要评分）</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>如果 AI 回复只讲题面或泛泛讲算法，没有回应学生当前问题，“是否贴合题目/对话”和“是否抓住卡点”应降分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>异常 C：AI 接了当前问题但没延续上一轮提示</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>上一轮 AI 提问/提示 + 学生当前问题 + AI 回复（要评分）</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>如果当前问题是学生对上一轮提示的回答，而 AI 没有顺着推进，可在“下一步是否清楚”“备注”里体现。</t>
         </is>
@@ -42317,7 +44814,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_271835fa3c</t>
+          <t>resp_1e76bd3c79</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -42406,29 +44903,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -43083,7 +45611,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_ce3430ca15</t>
+          <t>resp_2e87451f57</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -43184,29 +45712,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -43861,7 +46420,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_6646fa85b7</t>
+          <t>resp_be280eaafc</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -43956,29 +46515,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -44633,7 +47223,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_dce04287bd</t>
+          <t>resp_317903ec32</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -44726,29 +47316,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：当前主要问题不是算法桥，而是需要把请求重定向到一个可学习的最小下一步。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要给出完整题解或完整思路
+- 不要给出完整可提交代码
+- 不要直接确认完整答案/算法路线</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复明确不直接给完整答案或完整代码。
+- 回复要求学生补充当前思路、最小代码片段或具体卡点。
+- 回复提供一个安全的下一步而不是惩罚学生。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>policy_direct_answer_special</t>
+          <t>策略请求：直接要答案/代码</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>safe_redirect</t>
+          <t>安全重定向</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -45403,7 +48024,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_6eb2ccab34</t>
+          <t>resp_6404042cb7</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -45500,29 +48121,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -46177,7 +48829,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_cdb7ce8d5c</t>
+          <t>resp_0db1817a15</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -46267,29 +48919,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -46944,7 +49627,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_f4591e4e29</t>
+          <t>resp_755240f381</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -47027,29 +49710,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -47696,7 +50410,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_8028ab808d</t>
+          <t>resp_b2f2d2476e</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -47788,29 +50502,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少根据题目允许的动作、选择或依赖关系反推转移来源。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整转移或递推关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复引导学生列出当前一步可由哪些更小子问题产生。
+- 回复让学生先分析一个选择分支或一个前驱来源。
+- 回复不直接写完整递推式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -48457,7 +51202,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_9e3362e1ff</t>
+          <t>resp_b138d84957</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -48547,29 +51292,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+- 回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+- 回复不直接给完整背包模板或循环方向结论。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环方向、上一轮旧值和本轮新值复用风险对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+- 回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+- 回复不直接给完整背包模板或循环方向结论。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -49224,7 +52000,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_9d0f4a61d6</t>
+          <t>resp_c19ba3145b</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -49313,29 +52089,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+- 回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+- 回复不直接给完整代码、整张字符映射表或整题总做法。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接给出完整按键映射表</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面中的单个字符（字母或空格）映射到按键次数，并把输入逐字符累计的实现桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路
+- 不要直接给出完整按键映射表</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+- 回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+- 回复不直接给完整代码、整张字符映射表或整题总做法。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -50442,7 +53249,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_1a89782c2a</t>
+          <t>resp_c1703bea82</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -50547,29 +53354,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update 后哪些前缀/摘要信息应随之改变。
+- 回复用一个极小数组检查 query 需要从哪些维护量组合出区间和。
+- 回复不直接给完整树状数组模板或完整 lowbit 操作序列。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把单点修改、前缀和查询以及数据结构内部维护的摘要量对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update 后哪些前缀/摘要信息应随之改变。
+- 回复用一个极小数组检查 query 需要从哪些维护量组合出区间和。
+- 回复不直接给完整树状数组模板或完整 lowbit 操作序列。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -51224,7 +54062,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_2b76a7077c</t>
+          <t>resp_e080ab04b3</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -51316,29 +54154,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -51996,7 +54865,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_18c400626b</t>
+          <t>resp_efbdc5d54e</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -52093,29 +54962,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -52770,7 +55670,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_58dc28c0db</t>
+          <t>resp_b3a455b71f</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -52868,29 +55768,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少从题面对象关系到图、树、状态空间或约束结构的建模映射。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整建模映射或对象关系
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先列出题面中的对象和一种关系。
+- 回复引导学生判断这个关系适合表示为边、状态转移还是约束。
+- 回复不直接给完整建模方案。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -53545,7 +56476,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_5eb05f77bd</t>
+          <t>resp_223aeebd7a</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -53643,29 +56574,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把循环不变量、已处理范围和更新方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整边界更新或循环方向规则
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
+- 回复用一个很小范围检查边界或顺序含义。
+- 回复不直接给完整模板或边界更新公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_partial_answer</t>
+          <t>部分跟上：回答不完整后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>clarify</t>
+          <t>澄清当前回答</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -54320,7 +57282,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_022dc36be8</t>
+          <t>resp_0f7146b55f</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -54443,29 +57405,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把一次局部影响转化为标记、差分或前缀汇总的贡献关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整标记/差分/贡献公式
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先追踪一个操作对少量位置或节点的影响。
+- 回复引导学生区分直接影响点和需要抵消/汇总的位置。
+- 回复不直接给完整加减标记公式。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_wrong_answer</t>
+          <t>跟得吃力：回答错误后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F3 比较难跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -55120,7 +58113,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_781f0e54ae</t>
+          <t>resp_e5a50f1ac5</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -55234,29 +58227,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把数据结构节点、集合或队列中的值与题目需要查询/更新的信息对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整数据结构操作序列或维护步骤
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说明一次 update/query 后应保持什么摘要不变量。
+- 回复用一个极小局部操作检查维护语义。
+- 回复不直接给完整数据结构操作模板。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_code_attempt</t>
+          <t>部分跟上：代码尝试后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F2 勉强/部分跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -56321,7 +59345,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_864ae6cae6</t>
+          <t>resp_def0d754c1</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -56420,29 +59444,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把错误现象转化为最小反例、中间变量检查或不变量验证的调试证据桥。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接指出并修完具体 bug
+- 不要直接给出完整代码补丁
+- 不要给出完整题解或完整思路</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生构造或手算一个极小反例。
+- 回复要求学生检查一个中间变量或一步状态。
+- 回复不直接指出完整修法。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_prerequisite_gap</t>
+          <t>基础断层：前置概念缺口后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F4 基础断层</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>prerequisite_repair</t>
+          <t>补前置概念</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -57097,7 +60152,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_291ed22177</t>
+          <t>resp_38de155161</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -57192,29 +60247,60 @@
           <t>no_recent_dialogue</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把题面对象、已处理范围和状态值语义对应起来的表示关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整状态/表示定义
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生先说清状态下标代表的对象或范围。
+- 回复让学生区分状态值记录的是目标、可行性、数量还是代价。
+- 回复不直接给出完整状态定义。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>initial_question</t>
+          <t>初始提问</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>micro_step</t>
+          <t>拆成更小一步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr"/>
@@ -57861,7 +60947,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>resp_f311cc8862</t>
+          <t>resp_a42ada0f17</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -57948,29 +61034,60 @@
           <t>aligned_prior_context_ends_with_assistant</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>如果回复直接说出或完整推导出当前关键桥：缺少把候选值、题目限制和可行性判断方向对应起来的关系。，通常应判为关键桥泄露。
+尤其要避免命中“本轮禁止补完”中的内容：
+- 不要直接给出完整 check/判定条件
+- 不要给出完整题解或完整思路
+- 不要直接补完当前关键桥</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>可以复述题意、确认学生已经说出的内容、指出观察方向、给一个未完整演算的局部问题或微任务；可以提示应比较哪些对象或变量，但不要替学生完整补完当前关键桥、完整公式、完整规则或完整代码。</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>学生下一步应能围绕成功标准做一个短回答或局部判断：
+- 回复让学生用极小候选值判断条件是否满足。
+- 回复让学生说明 true/false 分别意味着保留哪一侧可能性。
+- 回复不直接给出完整 check 条件。</t>
+        </is>
+      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>后续辅导轮</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>能跟上：短答正确后续轮</t>
         </is>
       </c>
       <c r="X3" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 能一直跟上</t>
         </is>
       </c>
       <c r="Y3" s="6" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>推进到下一小步</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
